--- a/Base de Datos.xlsx
+++ b/Base de Datos.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Personal\OneDrive\Desktop\Proyecto_Django\mysite\ProyectoEmpresa\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Personal\OneDrive\Desktop\Contabilidad\Proyecto_Django\mysite\ProyectoEmpresa\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8B56A9F-DFF5-4D7E-A1E0-97947A9A02D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8AA4423-1EA5-4B61-BA3D-702CE460751C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A2C483C5-9B39-4EAD-8E99-D5293AD625C3}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>NOMINA DE LA EMPRESA Z</t>
   </si>
@@ -99,6 +99,12 @@
   </si>
   <si>
     <t>VENDEDOR B</t>
+  </si>
+  <si>
+    <t>Juan</t>
+  </si>
+  <si>
+    <t>Estudiante</t>
   </si>
 </sst>
 </file>
@@ -217,7 +223,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -238,6 +244,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -553,7 +560,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{981517B1-4BD8-4CEF-A3A7-2FB984670DA8}">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.109375" bestFit="1" customWidth="1"/>
@@ -728,6 +735,26 @@
         <v>450</v>
       </c>
     </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="3">
+        <v>8</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="4">
+        <v>1234</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11" s="8">
+        <v>46068</v>
+      </c>
+      <c r="F11" s="10">
+        <v>200</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
